--- a/site/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/headings.xlsx
+++ b/site/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,29 +771,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>User Provision Threshold Settings</t>
+          <t>Manage Group</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01KF2STBQHQZSSRVHSD95EW224</t>
+          <t>01KF312TPQQR7M1EQ9PP7Z2WE7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01KF2STBQHQZSSRVHSD95EW224</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01KF312TPQQR7M1EQ9PP7Z2WE7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Manage Group</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01KF312TPQQR7M1EQ9PP7Z2WE7</t>
+          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01KF312TPQQR7M1EQ9PP7Z2WE7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,63 +825,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01K5TXWEG9QVYTG8WCYTN8SJ58</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01K5TXWEG9QVYTG8WCYTN8SJ58</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,107 +913,107 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Insight Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Group Rules</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,63 +1045,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,54 +1111,10 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Brivo-Security-Suite-Paylocity-Event-Based-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
